--- a/black-tower-en_scenes.xlsx
+++ b/black-tower-en_scenes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Leonov\black-tower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0084D8D9-08EE-4FF9-BD91-7B61F2BC3A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C1A68E-4073-4F89-9C46-467B83BBD3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="1212">
   <si>
     <t>ID</t>
   </si>
@@ -2197,9 +2197,6 @@
 spotted by the Eagle—a sentry atop one of the towers—and a small detachment
 of 15–20 Goblins came out of the castle to intercept you. The fight in the forest was chaotic, but short.
 The order—to destroy the spy—they carried out...</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t xml:space="preserve">     You put a ring with a ruby on your finger (+  49). Alas, you can no longer manage
@@ -9850,9 +9847,7 @@
       <c r="B196" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>389</v>
-      </c>
+      <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
@@ -9862,17 +9857,17 @@
         <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="D197" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="57.35" x14ac:dyDescent="0.5">
@@ -9880,10 +9875,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
@@ -9894,10 +9889,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
@@ -9908,10 +9903,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
@@ -9922,7 +9917,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>201</v>
@@ -9936,10 +9931,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
@@ -9950,10 +9945,10 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
@@ -9964,10 +9959,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
@@ -9978,10 +9973,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
@@ -9992,10 +9987,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
@@ -10006,10 +10001,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
@@ -10020,10 +10015,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
@@ -10034,10 +10029,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
@@ -10048,10 +10043,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
@@ -10062,10 +10057,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
@@ -10076,10 +10071,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
@@ -10090,10 +10085,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
@@ -10104,10 +10099,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
@@ -10118,10 +10113,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -10132,14 +10127,14 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F216" s="2"/>
     </row>
@@ -10148,10 +10143,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
@@ -10162,10 +10157,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
@@ -10176,10 +10171,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -10190,10 +10185,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
@@ -10204,10 +10199,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C221" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
@@ -10218,10 +10213,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C222" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
@@ -10232,7 +10227,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>247</v>
@@ -10246,10 +10241,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
@@ -10260,10 +10255,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
@@ -10274,7 +10269,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>292</v>
@@ -10288,7 +10283,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>98</v>
@@ -10302,7 +10297,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>137</v>
@@ -10316,10 +10311,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
@@ -10330,10 +10325,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C230" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
@@ -10344,10 +10339,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -10358,7 +10353,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>352</v>
@@ -10372,10 +10367,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
@@ -10386,10 +10381,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
@@ -10400,10 +10395,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -10414,10 +10409,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
@@ -10428,10 +10423,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
@@ -10442,10 +10437,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
@@ -10456,10 +10451,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -10470,17 +10465,17 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="D240" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.5">
@@ -10488,10 +10483,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C241" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
@@ -10502,10 +10497,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
@@ -10516,10 +10511,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
@@ -10530,14 +10525,14 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F244" s="2"/>
     </row>
@@ -10546,7 +10541,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>337</v>
@@ -10560,7 +10555,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>219</v>
@@ -10574,10 +10569,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
@@ -10588,14 +10583,14 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F248" s="2"/>
     </row>
@@ -10604,7 +10599,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -10616,10 +10611,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
@@ -10630,10 +10625,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C251" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
@@ -10644,10 +10639,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
@@ -10658,10 +10653,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
@@ -10672,10 +10667,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
@@ -10686,10 +10681,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
@@ -10700,10 +10695,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
@@ -10714,10 +10709,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
@@ -10728,14 +10723,14 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F258" s="2"/>
     </row>
@@ -10744,17 +10739,17 @@
         <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="D259" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="28.7" x14ac:dyDescent="0.5">
@@ -10762,7 +10757,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>255</v>
@@ -10776,10 +10771,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
@@ -10790,10 +10785,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
@@ -10804,7 +10799,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>332</v>
@@ -10818,10 +10813,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
@@ -10832,14 +10827,14 @@
         <v>264</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F265" s="2"/>
     </row>
@@ -10848,10 +10843,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
@@ -10862,10 +10857,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
@@ -10876,17 +10871,17 @@
         <v>267</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="43" x14ac:dyDescent="0.5">
@@ -10894,10 +10889,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
@@ -10908,7 +10903,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>198</v>
@@ -10922,10 +10917,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
@@ -10936,7 +10931,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>219</v>
@@ -10950,7 +10945,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>160</v>
@@ -10964,10 +10959,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
@@ -10978,10 +10973,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
@@ -10992,10 +10987,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C276" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
@@ -11006,7 +11001,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
@@ -11018,10 +11013,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
@@ -11032,7 +11027,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>98</v>
@@ -11046,10 +11041,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
@@ -11060,10 +11055,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
@@ -11074,13 +11069,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
@@ -11090,10 +11085,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
@@ -11104,10 +11099,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C284" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
@@ -11118,10 +11113,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C285" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
@@ -11132,10 +11127,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
@@ -11146,10 +11141,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
@@ -11160,10 +11155,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
@@ -11174,10 +11169,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
@@ -11188,7 +11183,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>352</v>
@@ -11202,16 +11197,16 @@
         <v>290</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="D291" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D291" s="2" t="s">
+      <c r="E291" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="F291" s="2"/>
     </row>
@@ -11220,10 +11215,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
@@ -11234,10 +11229,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
@@ -11248,10 +11243,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
@@ -11262,7 +11257,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>124</v>
@@ -11276,7 +11271,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>342</v>
@@ -11290,13 +11285,13 @@
         <v>296</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="C297" s="2" t="s">
+      <c r="D297" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
@@ -11306,10 +11301,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
@@ -11320,7 +11315,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>158</v>
@@ -11334,10 +11329,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
@@ -11348,10 +11343,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C301" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
@@ -11362,10 +11357,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C302" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
@@ -11376,10 +11371,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C303" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
@@ -11390,10 +11385,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C304" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
@@ -11404,10 +11399,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C305" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
@@ -11418,7 +11413,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>205</v>
@@ -11432,7 +11427,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" s="2"/>
@@ -11444,10 +11439,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
@@ -11458,10 +11453,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C309" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>603</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
@@ -11472,10 +11467,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" s="2" t="s">
@@ -11488,10 +11483,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C311" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
@@ -11502,10 +11497,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C312" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
@@ -11516,10 +11511,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
@@ -11530,7 +11525,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>24</v>
@@ -11544,7 +11539,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>83</v>
@@ -11558,7 +11553,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>98</v>
@@ -11572,14 +11567,14 @@
         <v>316</v>
       </c>
       <c r="B317" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C317" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F317" s="2"/>
     </row>
@@ -11588,10 +11583,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C318" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
@@ -11602,10 +11597,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C319" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
@@ -11616,10 +11611,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
@@ -11630,10 +11625,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C321" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
@@ -11644,10 +11639,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C322" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
@@ -11658,10 +11653,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C323" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="C323" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
@@ -11672,10 +11667,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C324" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
@@ -11686,10 +11681,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C325" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
@@ -11700,7 +11695,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>198</v>
@@ -11714,14 +11709,14 @@
         <v>326</v>
       </c>
       <c r="B327" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C327" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F327" s="2"/>
     </row>
@@ -11730,10 +11725,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
@@ -11744,14 +11739,14 @@
         <v>328</v>
       </c>
       <c r="B329" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C329" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F329" s="2"/>
     </row>
@@ -11760,10 +11755,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" s="2"/>
@@ -11774,7 +11769,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
@@ -11786,7 +11781,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>387</v>
@@ -11800,10 +11795,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C333" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" s="2"/>
@@ -11814,10 +11809,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C334" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="C334" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" s="2"/>
@@ -11828,10 +11823,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="C335" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" s="2"/>
@@ -11842,17 +11837,17 @@
         <v>335</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E336" s="2"/>
       <c r="F336" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="337" spans="1:6" ht="57.35" x14ac:dyDescent="0.5">
@@ -11860,17 +11855,17 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C337" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C337" s="2" t="s">
+      <c r="D337" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="D337" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="E337" s="2"/>
       <c r="F337" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="338" spans="1:6" ht="57.35" x14ac:dyDescent="0.5">
@@ -11878,10 +11873,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C338" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
@@ -11892,10 +11887,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C339" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
@@ -11906,10 +11901,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
@@ -11920,10 +11915,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C341" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
@@ -11934,10 +11929,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C342" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
@@ -11948,7 +11943,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>131</v>
@@ -11962,10 +11957,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C344" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="C344" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" s="2"/>
@@ -11976,7 +11971,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>95</v>
@@ -11990,10 +11985,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
@@ -12004,10 +11999,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="C347" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
@@ -12018,7 +12013,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
@@ -12030,10 +12025,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
@@ -12044,13 +12039,13 @@
         <v>349</v>
       </c>
       <c r="B350" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="C350" s="2" t="s">
+      <c r="D350" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D350" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
@@ -12060,10 +12055,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C351" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C351" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
@@ -12074,10 +12069,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C352" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
@@ -12088,7 +12083,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>170</v>
@@ -12102,10 +12097,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
@@ -12116,10 +12111,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
@@ -12130,10 +12125,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" s="2"/>
@@ -12144,19 +12139,19 @@
         <v>356</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D357" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E357" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="E357" s="2" t="s">
+      <c r="F357" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="358" spans="1:6" ht="28.7" x14ac:dyDescent="0.5">
@@ -12164,10 +12159,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" s="2"/>
@@ -12178,10 +12173,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" s="2"/>
@@ -12192,7 +12187,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C360" s="2"/>
       <c r="D360" s="2"/>
@@ -12204,10 +12199,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C361" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
@@ -12218,7 +12213,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" s="2"/>
@@ -12230,7 +12225,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>201</v>
@@ -12244,10 +12239,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C364" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
@@ -12258,7 +12253,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>160</v>
@@ -12272,10 +12267,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" s="2"/>
@@ -12286,10 +12281,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C367" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
@@ -12300,17 +12295,17 @@
         <v>367</v>
       </c>
       <c r="B368" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C368" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="C368" s="2" t="s">
+      <c r="D368" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="D368" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="E368" s="2"/>
       <c r="F368" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="369" spans="1:6" ht="43" x14ac:dyDescent="0.5">
@@ -12318,7 +12313,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" s="2"/>
@@ -12330,10 +12325,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
@@ -12344,10 +12339,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="C371" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" s="2"/>
@@ -12358,10 +12353,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C372" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" s="2"/>
@@ -12372,7 +12367,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>131</v>
@@ -12386,10 +12381,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C374" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" s="2"/>
@@ -12400,14 +12395,14 @@
         <v>374</v>
       </c>
       <c r="B375" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C375" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="C375" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F375" s="2"/>
     </row>
@@ -12416,10 +12411,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C376" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="C376" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" s="2"/>
@@ -12430,10 +12425,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C377" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="C377" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" s="2"/>
@@ -12444,10 +12439,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C378" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="C378" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" s="2"/>
@@ -12458,10 +12453,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C379" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="C379" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" s="2"/>
@@ -12472,10 +12467,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" s="2"/>
@@ -12486,10 +12481,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C381" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="C381" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" s="2"/>
@@ -12500,10 +12495,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C382" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="C382" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" s="2"/>
@@ -12514,10 +12509,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C383" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="C383" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" s="2"/>
@@ -12528,10 +12523,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C384" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="C384" s="2" t="s">
-        <v>739</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" s="2"/>
@@ -12542,17 +12537,17 @@
         <v>384</v>
       </c>
       <c r="B385" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="C385" s="2" t="s">
+      <c r="D385" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>742</v>
       </c>
       <c r="E385" s="2"/>
       <c r="F385" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="386" spans="1:6" ht="43" x14ac:dyDescent="0.5">
@@ -12560,10 +12555,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" s="2"/>
@@ -12574,10 +12569,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C387" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>746</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" s="2"/>
@@ -12588,7 +12583,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>77</v>
@@ -12602,10 +12597,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C389" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="C389" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" s="2"/>
@@ -12616,10 +12611,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C390" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="C390" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" s="2"/>
@@ -12630,7 +12625,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" s="2"/>
@@ -12642,10 +12637,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" s="2"/>
@@ -12656,7 +12651,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C393" s="2"/>
       <c r="D393" s="2"/>
@@ -12668,10 +12663,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" s="2"/>
@@ -12682,10 +12677,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" s="2"/>
@@ -12696,10 +12691,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" s="2"/>
@@ -12710,7 +12705,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>332</v>
@@ -12724,10 +12719,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="C398" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="C398" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" s="2"/>
@@ -12738,7 +12733,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>193</v>
@@ -12752,10 +12747,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C400" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" s="2"/>
@@ -12766,7 +12761,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>387</v>
@@ -12780,10 +12775,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C402" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" s="2"/>
@@ -12794,7 +12789,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>177</v>
@@ -12808,10 +12803,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C404" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="C404" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" s="2"/>
@@ -12822,10 +12817,10 @@
         <v>404</v>
       </c>
       <c r="B405" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C405" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" s="2"/>
@@ -12836,7 +12831,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>201</v>
@@ -12850,10 +12845,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>773</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>774</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" s="2"/>
@@ -12864,7 +12859,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C408" s="2" t="s">
         <v>131</v>
@@ -12878,17 +12873,17 @@
         <v>408</v>
       </c>
       <c r="B409" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C409" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="C409" s="2" t="s">
+      <c r="D409" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>778</v>
       </c>
       <c r="E409" s="2"/>
       <c r="F409" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="410" spans="1:6" ht="186.35" x14ac:dyDescent="0.5">
@@ -12896,10 +12891,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C410" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" s="2"/>
@@ -12910,10 +12905,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C411" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" s="2"/>
@@ -12924,10 +12919,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C412" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" s="2"/>
@@ -12938,10 +12933,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C413" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" s="2"/>
@@ -12952,10 +12947,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" s="2"/>
@@ -12966,17 +12961,17 @@
         <v>414</v>
       </c>
       <c r="B415" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C415" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="C415" s="2" t="s">
+      <c r="D415" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D415" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="E415" s="2"/>
       <c r="F415" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="416" spans="1:6" ht="28.7" x14ac:dyDescent="0.5">
@@ -12984,10 +12979,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C416" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" s="2"/>
@@ -12998,10 +12993,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C417" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>796</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" s="2"/>
@@ -13012,10 +13007,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C418" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" s="2"/>
@@ -13026,10 +13021,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" s="2"/>
@@ -13040,10 +13035,10 @@
         <v>419</v>
       </c>
       <c r="B420" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C420" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="C420" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" s="2"/>
@@ -13054,10 +13049,10 @@
         <v>420</v>
       </c>
       <c r="B421" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C421" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="C421" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" s="2"/>
@@ -13068,10 +13063,10 @@
         <v>421</v>
       </c>
       <c r="B422" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C422" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="C422" s="2" t="s">
-        <v>805</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" s="2"/>
@@ -13082,10 +13077,10 @@
         <v>422</v>
       </c>
       <c r="B423" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C423" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" s="2"/>
@@ -13096,10 +13091,10 @@
         <v>423</v>
       </c>
       <c r="B424" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C424" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="C424" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" s="2"/>
@@ -13110,10 +13105,10 @@
         <v>424</v>
       </c>
       <c r="B425" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C425" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>811</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" s="2"/>
@@ -13124,10 +13119,10 @@
         <v>425</v>
       </c>
       <c r="B426" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C426" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="C426" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" s="2"/>
@@ -13138,10 +13133,10 @@
         <v>426</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" s="2"/>
@@ -13152,10 +13147,10 @@
         <v>427</v>
       </c>
       <c r="B428" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C428" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="C428" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" s="2"/>
@@ -13166,10 +13161,10 @@
         <v>428</v>
       </c>
       <c r="B429" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C429" s="2" t="s">
         <v>817</v>
-      </c>
-      <c r="C429" s="2" t="s">
-        <v>818</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" s="2"/>
@@ -13180,7 +13175,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>195</v>
@@ -13194,7 +13189,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>131</v>
@@ -13208,10 +13203,10 @@
         <v>431</v>
       </c>
       <c r="B432" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C432" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="C432" s="2" t="s">
-        <v>822</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" s="2"/>
@@ -13222,10 +13217,10 @@
         <v>432</v>
       </c>
       <c r="B433" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C433" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="C433" s="2" t="s">
-        <v>824</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" s="2"/>
@@ -13236,17 +13231,17 @@
         <v>433</v>
       </c>
       <c r="B434" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C434" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="C434" s="2" t="s">
+      <c r="D434" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="D434" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="E434" s="2"/>
       <c r="F434" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="435" spans="1:6" ht="229.35" x14ac:dyDescent="0.5">
@@ -13254,10 +13249,10 @@
         <v>434</v>
       </c>
       <c r="B435" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C435" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="C435" s="2" t="s">
-        <v>830</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" s="2"/>
@@ -13268,10 +13263,10 @@
         <v>435</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" s="2"/>
@@ -13282,17 +13277,17 @@
         <v>436</v>
       </c>
       <c r="B437" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="D437" s="2" t="s">
         <v>832</v>
-      </c>
-      <c r="C437" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="D437" s="2" t="s">
-        <v>833</v>
       </c>
       <c r="E437" s="2"/>
       <c r="F437" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="438" spans="1:6" ht="71.7" x14ac:dyDescent="0.5">
@@ -13300,10 +13295,10 @@
         <v>437</v>
       </c>
       <c r="B438" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C438" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="C438" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" s="2"/>
@@ -13314,10 +13309,10 @@
         <v>438</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" s="2"/>
@@ -13328,10 +13323,10 @@
         <v>439</v>
       </c>
       <c r="B440" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C440" s="2" t="s">
         <v>837</v>
-      </c>
-      <c r="C440" s="2" t="s">
-        <v>838</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" s="2"/>
@@ -13342,10 +13337,10 @@
         <v>440</v>
       </c>
       <c r="B441" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="C441" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="C441" s="2" t="s">
-        <v>840</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" s="2"/>
@@ -13356,7 +13351,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>164</v>
@@ -13370,10 +13365,10 @@
         <v>442</v>
       </c>
       <c r="B443" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C443" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="C443" s="2" t="s">
-        <v>843</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" s="2"/>
@@ -13384,10 +13379,10 @@
         <v>443</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" s="2"/>
@@ -13398,10 +13393,10 @@
         <v>444</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" s="2"/>
@@ -13412,10 +13407,10 @@
         <v>445</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" s="2"/>
@@ -13426,10 +13421,10 @@
         <v>446</v>
       </c>
       <c r="B447" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C447" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="C447" s="2" t="s">
-        <v>848</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" s="2"/>
@@ -13440,10 +13435,10 @@
         <v>447</v>
       </c>
       <c r="B448" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C448" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="C448" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" s="2"/>
@@ -13454,17 +13449,17 @@
         <v>448</v>
       </c>
       <c r="B449" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C449" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="C449" s="2" t="s">
+      <c r="D449" s="2" t="s">
         <v>852</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>853</v>
       </c>
       <c r="E449" s="2"/>
       <c r="F449" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="450" spans="1:6" ht="43" x14ac:dyDescent="0.5">
@@ -13472,10 +13467,10 @@
         <v>449</v>
       </c>
       <c r="B450" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="C450" s="2" t="s">
         <v>855</v>
-      </c>
-      <c r="C450" s="2" t="s">
-        <v>856</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" s="2"/>
@@ -13486,10 +13481,10 @@
         <v>450</v>
       </c>
       <c r="B451" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C451" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="C451" s="2" t="s">
-        <v>858</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" s="2"/>
@@ -13500,10 +13495,10 @@
         <v>451</v>
       </c>
       <c r="B452" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="C452" s="2" t="s">
         <v>859</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>860</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" s="2"/>
@@ -13514,7 +13509,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>68</v>
@@ -13528,7 +13523,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>143</v>
@@ -13544,10 +13539,10 @@
         <v>454</v>
       </c>
       <c r="B455" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C455" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="C455" s="2" t="s">
-        <v>864</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" s="2"/>
@@ -13558,10 +13553,10 @@
         <v>455</v>
       </c>
       <c r="B456" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C456" s="2" t="s">
         <v>865</v>
-      </c>
-      <c r="C456" s="2" t="s">
-        <v>866</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" s="2"/>
@@ -13572,10 +13567,10 @@
         <v>456</v>
       </c>
       <c r="B457" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C457" s="2" t="s">
         <v>867</v>
-      </c>
-      <c r="C457" s="2" t="s">
-        <v>868</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" s="2"/>
@@ -13586,10 +13581,10 @@
         <v>457</v>
       </c>
       <c r="B458" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C458" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="C458" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" s="2"/>
@@ -13600,10 +13595,10 @@
         <v>458</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" s="2"/>
@@ -13614,10 +13609,10 @@
         <v>459</v>
       </c>
       <c r="B460" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C460" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="C460" s="2" t="s">
-        <v>873</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" s="2"/>
@@ -13628,10 +13623,10 @@
         <v>460</v>
       </c>
       <c r="B461" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C461" s="2" t="s">
         <v>874</v>
-      </c>
-      <c r="C461" s="2" t="s">
-        <v>875</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" s="2"/>
@@ -13642,7 +13637,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>47</v>
@@ -13656,10 +13651,10 @@
         <v>462</v>
       </c>
       <c r="B463" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C463" s="2" t="s">
         <v>877</v>
-      </c>
-      <c r="C463" s="2" t="s">
-        <v>878</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" s="2"/>
@@ -13670,10 +13665,10 @@
         <v>463</v>
       </c>
       <c r="B464" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C464" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="C464" s="2" t="s">
-        <v>880</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" s="2"/>
@@ -13684,13 +13679,13 @@
         <v>464</v>
       </c>
       <c r="B465" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C465" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="C465" s="2" t="s">
+      <c r="D465" s="2" t="s">
         <v>882</v>
-      </c>
-      <c r="D465" s="2" t="s">
-        <v>883</v>
       </c>
       <c r="E465" s="2"/>
       <c r="F465" s="2"/>
@@ -13700,10 +13695,10 @@
         <v>465</v>
       </c>
       <c r="B466" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="C466" s="2" t="s">
         <v>884</v>
-      </c>
-      <c r="C466" s="2" t="s">
-        <v>885</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" s="2"/>
@@ -13714,10 +13709,10 @@
         <v>466</v>
       </c>
       <c r="B467" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C467" s="2" t="s">
         <v>886</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>887</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" s="2"/>
@@ -13728,10 +13723,10 @@
         <v>467</v>
       </c>
       <c r="B468" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C468" s="2" t="s">
         <v>888</v>
-      </c>
-      <c r="C468" s="2" t="s">
-        <v>889</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" s="2"/>
@@ -13742,10 +13737,10 @@
         <v>468</v>
       </c>
       <c r="B469" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C469" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="C469" s="2" t="s">
-        <v>891</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" s="2"/>
@@ -13756,7 +13751,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>158</v>
@@ -13770,10 +13765,10 @@
         <v>470</v>
       </c>
       <c r="B471" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C471" s="2" t="s">
         <v>893</v>
-      </c>
-      <c r="C471" s="2" t="s">
-        <v>894</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" s="2"/>
@@ -13784,17 +13779,17 @@
         <v>471</v>
       </c>
       <c r="B472" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C472" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D472" s="2" t="s">
         <v>895</v>
-      </c>
-      <c r="C472" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D472" s="2" t="s">
-        <v>896</v>
       </c>
       <c r="E472" s="2"/>
       <c r="F472" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="473" spans="1:6" ht="57.35" x14ac:dyDescent="0.5">
@@ -13802,10 +13797,10 @@
         <v>472</v>
       </c>
       <c r="B473" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C473" s="2" t="s">
         <v>898</v>
-      </c>
-      <c r="C473" s="2" t="s">
-        <v>899</v>
       </c>
       <c r="D473" s="2"/>
       <c r="E473" s="2"/>
@@ -13816,7 +13811,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>332</v>
@@ -13830,10 +13825,10 @@
         <v>474</v>
       </c>
       <c r="B475" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="C475" s="2" t="s">
         <v>901</v>
-      </c>
-      <c r="C475" s="2" t="s">
-        <v>902</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" s="2"/>
@@ -13844,10 +13839,10 @@
         <v>475</v>
       </c>
       <c r="B476" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C476" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="C476" s="2" t="s">
-        <v>904</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" s="2"/>
@@ -13858,7 +13853,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C477" s="2" t="s">
         <v>340</v>
@@ -13872,10 +13867,10 @@
         <v>477</v>
       </c>
       <c r="B478" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C478" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="C478" s="2" t="s">
-        <v>907</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" s="2"/>
@@ -13886,10 +13881,10 @@
         <v>478</v>
       </c>
       <c r="B479" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C479" s="2" t="s">
         <v>908</v>
-      </c>
-      <c r="C479" s="2" t="s">
-        <v>909</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" s="2"/>
@@ -13900,10 +13895,10 @@
         <v>479</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" s="2"/>
@@ -13914,10 +13909,10 @@
         <v>480</v>
       </c>
       <c r="B481" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C481" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="C481" s="2" t="s">
-        <v>912</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" s="2"/>
@@ -13928,10 +13923,10 @@
         <v>481</v>
       </c>
       <c r="B482" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C482" s="2" t="s">
         <v>913</v>
-      </c>
-      <c r="C482" s="2" t="s">
-        <v>914</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" s="2"/>
@@ -13942,7 +13937,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>201</v>
@@ -13956,14 +13951,14 @@
         <v>483</v>
       </c>
       <c r="B484" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="C484" s="2" t="s">
         <v>916</v>
-      </c>
-      <c r="C484" s="2" t="s">
-        <v>917</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F484" s="2"/>
     </row>
@@ -13972,17 +13967,17 @@
         <v>484</v>
       </c>
       <c r="B485" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C485" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="C485" s="2" t="s">
+      <c r="D485" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="D485" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="E485" s="2"/>
       <c r="F485" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="486" spans="1:6" ht="57.35" x14ac:dyDescent="0.5">
@@ -13990,7 +13985,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>306</v>
@@ -14004,10 +13999,10 @@
         <v>486</v>
       </c>
       <c r="B487" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C487" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="C487" s="2" t="s">
-        <v>925</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" s="2"/>
@@ -14018,14 +14013,14 @@
         <v>487</v>
       </c>
       <c r="B488" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C488" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="C488" s="2" t="s">
-        <v>927</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F488" s="2"/>
     </row>
@@ -14034,7 +14029,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>95</v>
@@ -14048,10 +14043,10 @@
         <v>489</v>
       </c>
       <c r="B490" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C490" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="C490" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" s="2"/>
@@ -14062,10 +14057,10 @@
         <v>490</v>
       </c>
       <c r="B491" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="C491" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="C491" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" s="2"/>
@@ -14076,10 +14071,10 @@
         <v>491</v>
       </c>
       <c r="B492" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="C492" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="C492" s="2" t="s">
-        <v>935</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" s="2"/>
@@ -14090,10 +14085,10 @@
         <v>492</v>
       </c>
       <c r="B493" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C493" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" s="2"/>
@@ -14104,7 +14099,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C494" s="2"/>
       <c r="D494" s="2"/>
@@ -14116,7 +14111,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C495" s="2"/>
       <c r="D495" s="2"/>
@@ -14128,7 +14123,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>168</v>
@@ -14142,10 +14137,10 @@
         <v>496</v>
       </c>
       <c r="B497" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C497" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>942</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" s="2"/>
@@ -14156,10 +14151,10 @@
         <v>497</v>
       </c>
       <c r="B498" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C498" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="C498" s="2" t="s">
-        <v>944</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" s="2"/>
@@ -14170,10 +14165,10 @@
         <v>498</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" s="2"/>
@@ -14184,14 +14179,14 @@
         <v>499</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>255</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F500" s="2"/>
     </row>
@@ -14200,7 +14195,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>137</v>
@@ -14214,10 +14209,10 @@
         <v>501</v>
       </c>
       <c r="B502" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C502" s="2" t="s">
         <v>949</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>950</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" s="2"/>
@@ -14228,7 +14223,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C503" s="2"/>
       <c r="D503" s="2"/>
@@ -14240,10 +14235,10 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" s="2"/>
@@ -14254,10 +14249,10 @@
         <v>504</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" s="2"/>
@@ -14268,10 +14263,10 @@
         <v>505</v>
       </c>
       <c r="B506" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="C506" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="C506" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" s="2"/>
@@ -14282,7 +14277,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>332</v>
@@ -14296,10 +14291,10 @@
         <v>507</v>
       </c>
       <c r="B508" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C508" s="2" t="s">
         <v>957</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>958</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" s="2"/>
@@ -14310,10 +14305,10 @@
         <v>508</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" s="2"/>
@@ -14324,10 +14319,10 @@
         <v>509</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" s="2"/>
@@ -14338,10 +14333,10 @@
         <v>510</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" s="2"/>
@@ -14352,10 +14347,10 @@
         <v>511</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" s="2"/>
@@ -14366,7 +14361,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>98</v>
@@ -14380,10 +14375,10 @@
         <v>513</v>
       </c>
       <c r="B514" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C514" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="C514" s="2" t="s">
-        <v>965</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" s="2"/>
@@ -14394,10 +14389,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="C515" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="C515" s="2" t="s">
-        <v>967</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" s="2"/>
@@ -14408,7 +14403,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>146</v>
@@ -14422,10 +14417,10 @@
         <v>516</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" s="2"/>
@@ -14436,10 +14431,10 @@
         <v>517</v>
       </c>
       <c r="B518" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="C518" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="C518" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" s="2"/>
@@ -14450,14 +14445,14 @@
         <v>518</v>
       </c>
       <c r="B519" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C519" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C519" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F519" s="2"/>
     </row>
@@ -14466,10 +14461,10 @@
         <v>519</v>
       </c>
       <c r="B520" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C520" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="C520" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" s="2"/>
@@ -14480,17 +14475,17 @@
         <v>520</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E521" s="2"/>
       <c r="F521" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="522" spans="1:6" ht="57.35" x14ac:dyDescent="0.5">
@@ -14498,10 +14493,10 @@
         <v>521</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" s="2"/>
@@ -14512,10 +14507,10 @@
         <v>522</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" s="2"/>
@@ -14526,7 +14521,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>193</v>
@@ -14540,10 +14535,10 @@
         <v>524</v>
       </c>
       <c r="B525" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C525" s="2" t="s">
         <v>983</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>984</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" s="2"/>
@@ -14554,10 +14549,10 @@
         <v>525</v>
       </c>
       <c r="B526" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C526" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="C526" s="2" t="s">
-        <v>986</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" s="2"/>
@@ -14568,10 +14563,10 @@
         <v>526</v>
       </c>
       <c r="B527" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="C527" s="2" t="s">
         <v>987</v>
-      </c>
-      <c r="C527" s="2" t="s">
-        <v>988</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" s="2"/>
@@ -14582,10 +14577,10 @@
         <v>527</v>
       </c>
       <c r="B528" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="C528" s="2" t="s">
         <v>989</v>
-      </c>
-      <c r="C528" s="2" t="s">
-        <v>990</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" s="2"/>
@@ -14596,16 +14591,16 @@
         <v>528</v>
       </c>
       <c r="B529" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C529" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="C529" s="2" t="s">
+      <c r="D529" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="D529" s="2" t="s">
+      <c r="E529" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="E529" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="F529" s="2"/>
     </row>
@@ -14614,14 +14609,14 @@
         <v>529</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F530" s="2"/>
     </row>
@@ -14630,10 +14625,10 @@
         <v>530</v>
       </c>
       <c r="B531" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="C531" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="C531" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" s="2"/>
@@ -14644,10 +14639,10 @@
         <v>531</v>
       </c>
       <c r="B532" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C532" s="2" t="s">
         <v>999</v>
-      </c>
-      <c r="C532" s="2" t="s">
-        <v>1000</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" s="2"/>
@@ -14658,14 +14653,14 @@
         <v>532</v>
       </c>
       <c r="B533" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C533" s="2" t="s">
         <v>1001</v>
-      </c>
-      <c r="C533" s="2" t="s">
-        <v>1002</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F533" s="2"/>
     </row>
@@ -14674,10 +14669,10 @@
         <v>533</v>
       </c>
       <c r="B534" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C534" s="2" t="s">
         <v>1004</v>
-      </c>
-      <c r="C534" s="2" t="s">
-        <v>1005</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" s="2"/>
@@ -14688,10 +14683,10 @@
         <v>534</v>
       </c>
       <c r="B535" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C535" s="2" t="s">
         <v>1006</v>
-      </c>
-      <c r="C535" s="2" t="s">
-        <v>1007</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" s="2"/>
@@ -14702,10 +14697,10 @@
         <v>535</v>
       </c>
       <c r="B536" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C536" s="2" t="s">
         <v>1008</v>
-      </c>
-      <c r="C536" s="2" t="s">
-        <v>1009</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" s="2"/>
@@ -14716,10 +14711,10 @@
         <v>536</v>
       </c>
       <c r="B537" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C537" s="2" t="s">
         <v>1010</v>
-      </c>
-      <c r="C537" s="2" t="s">
-        <v>1011</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" s="2"/>
@@ -14730,10 +14725,10 @@
         <v>537</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" s="2"/>
@@ -14744,10 +14739,10 @@
         <v>538</v>
       </c>
       <c r="B539" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C539" s="2" t="s">
         <v>1013</v>
-      </c>
-      <c r="C539" s="2" t="s">
-        <v>1014</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" s="2"/>
@@ -14758,14 +14753,14 @@
         <v>539</v>
       </c>
       <c r="B540" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C540" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="C540" s="2" t="s">
-        <v>1016</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F540" s="2"/>
     </row>
@@ -14774,10 +14769,10 @@
         <v>540</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" s="2"/>
@@ -14788,10 +14783,10 @@
         <v>541</v>
       </c>
       <c r="B542" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C542" s="2" t="s">
         <v>1019</v>
-      </c>
-      <c r="C542" s="2" t="s">
-        <v>1020</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" s="2"/>
@@ -14802,10 +14797,10 @@
         <v>542</v>
       </c>
       <c r="B543" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C543" s="2" t="s">
         <v>1021</v>
-      </c>
-      <c r="C543" s="2" t="s">
-        <v>1022</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" s="2"/>
@@ -14816,14 +14811,14 @@
         <v>543</v>
       </c>
       <c r="B544" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C544" s="2" t="s">
         <v>1023</v>
-      </c>
-      <c r="C544" s="2" t="s">
-        <v>1024</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="F544" s="2"/>
     </row>
@@ -14832,10 +14827,10 @@
         <v>544</v>
       </c>
       <c r="B545" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C545" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="C545" s="2" t="s">
-        <v>1027</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" s="2"/>
@@ -14846,10 +14841,10 @@
         <v>545</v>
       </c>
       <c r="B546" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C546" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="C546" s="2" t="s">
-        <v>1029</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" s="2"/>
@@ -14860,7 +14855,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>131</v>
@@ -14874,10 +14869,10 @@
         <v>547</v>
       </c>
       <c r="B548" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C548" s="2" t="s">
         <v>1031</v>
-      </c>
-      <c r="C548" s="2" t="s">
-        <v>1032</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" s="2"/>
@@ -14888,10 +14883,10 @@
         <v>548</v>
       </c>
       <c r="B549" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C549" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="C549" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" s="2"/>
@@ -14902,10 +14897,10 @@
         <v>549</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" s="2"/>
@@ -14916,10 +14911,10 @@
         <v>550</v>
       </c>
       <c r="B551" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C551" s="2" t="s">
         <v>1036</v>
-      </c>
-      <c r="C551" s="2" t="s">
-        <v>1037</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" s="2"/>
@@ -14930,10 +14925,10 @@
         <v>551</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" s="2"/>
@@ -14944,10 +14939,10 @@
         <v>552</v>
       </c>
       <c r="B553" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C553" s="2" t="s">
         <v>1039</v>
-      </c>
-      <c r="C553" s="2" t="s">
-        <v>1040</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" s="2"/>
@@ -14958,14 +14953,14 @@
         <v>553</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F554" s="2"/>
     </row>
@@ -14974,7 +14969,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>195</v>
@@ -14988,10 +14983,10 @@
         <v>555</v>
       </c>
       <c r="B556" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C556" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="C556" s="2" t="s">
-        <v>1045</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" s="2"/>
@@ -15002,10 +14997,10 @@
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C557" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" s="2"/>
@@ -15016,10 +15011,10 @@
         <v>557</v>
       </c>
       <c r="B558" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C558" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="C558" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" s="2"/>
@@ -15030,14 +15025,14 @@
         <v>558</v>
       </c>
       <c r="B559" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C559" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="C559" s="2" t="s">
-        <v>1051</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F559" s="2"/>
     </row>
@@ -15046,10 +15041,10 @@
         <v>559</v>
       </c>
       <c r="B560" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C560" s="2" t="s">
         <v>1053</v>
-      </c>
-      <c r="C560" s="2" t="s">
-        <v>1054</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" s="2"/>
@@ -15060,10 +15055,10 @@
         <v>560</v>
       </c>
       <c r="B561" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C561" s="2" t="s">
         <v>1055</v>
-      </c>
-      <c r="C561" s="2" t="s">
-        <v>1056</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" s="2"/>
@@ -15074,10 +15069,10 @@
         <v>561</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" s="2"/>
@@ -15088,10 +15083,10 @@
         <v>562</v>
       </c>
       <c r="B563" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C563" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="C563" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" s="2"/>
@@ -15102,19 +15097,19 @@
         <v>563</v>
       </c>
       <c r="B564" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C564" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D564" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="C564" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D564" s="2" t="s">
+      <c r="E564" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="E564" s="2" t="s">
+      <c r="F564" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="F564" s="2" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="565" spans="1:6" ht="43" x14ac:dyDescent="0.5">
@@ -15122,7 +15117,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>160</v>
@@ -15136,10 +15131,10 @@
         <v>565</v>
       </c>
       <c r="B566" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C566" s="2" t="s">
         <v>1065</v>
-      </c>
-      <c r="C566" s="2" t="s">
-        <v>1066</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" s="2"/>
@@ -15150,10 +15145,10 @@
         <v>566</v>
       </c>
       <c r="B567" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C567" s="2" t="s">
         <v>1067</v>
-      </c>
-      <c r="C567" s="2" t="s">
-        <v>1068</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" s="2"/>
@@ -15164,14 +15159,14 @@
         <v>567</v>
       </c>
       <c r="B568" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C568" s="2" t="s">
         <v>1069</v>
-      </c>
-      <c r="C568" s="2" t="s">
-        <v>1070</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F568" s="2"/>
     </row>
@@ -15180,7 +15175,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C569" s="2"/>
       <c r="D569" s="2"/>
@@ -15192,10 +15187,10 @@
         <v>569</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" s="2"/>
@@ -15206,10 +15201,10 @@
         <v>570</v>
       </c>
       <c r="B571" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C571" s="2" t="s">
         <v>1074</v>
-      </c>
-      <c r="C571" s="2" t="s">
-        <v>1075</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" s="2"/>
@@ -15220,10 +15215,10 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C572" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="C572" s="2" t="s">
-        <v>1077</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" s="2"/>
@@ -15234,7 +15229,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C573" s="2"/>
       <c r="D573" s="2"/>
@@ -15246,17 +15241,17 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C574" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="C574" s="2" t="s">
+      <c r="D574" s="2" t="s">
         <v>1080</v>
-      </c>
-      <c r="D574" s="2" t="s">
-        <v>1081</v>
       </c>
       <c r="E574" s="2"/>
       <c r="F574" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="575" spans="1:6" ht="129" x14ac:dyDescent="0.5">
@@ -15264,10 +15259,10 @@
         <v>574</v>
       </c>
       <c r="B575" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C575" s="2" t="s">
         <v>1083</v>
-      </c>
-      <c r="C575" s="2" t="s">
-        <v>1084</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" s="2"/>
@@ -15278,10 +15273,10 @@
         <v>575</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" s="2"/>
@@ -15292,7 +15287,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>310</v>
@@ -15306,10 +15301,10 @@
         <v>577</v>
       </c>
       <c r="B578" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C578" s="2" t="s">
         <v>1087</v>
-      </c>
-      <c r="C578" s="2" t="s">
-        <v>1088</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" s="2"/>
@@ -15320,10 +15315,10 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C579" s="2" t="s">
         <v>1089</v>
-      </c>
-      <c r="C579" s="2" t="s">
-        <v>1090</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" s="2"/>
@@ -15334,7 +15329,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C580" s="2"/>
       <c r="D580" s="2"/>
@@ -15346,10 +15341,10 @@
         <v>580</v>
       </c>
       <c r="B581" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C581" s="2" t="s">
         <v>1092</v>
-      </c>
-      <c r="C581" s="2" t="s">
-        <v>1093</v>
       </c>
       <c r="D581" s="2"/>
       <c r="E581" s="2"/>
@@ -15360,7 +15355,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C582" s="2"/>
       <c r="D582" s="2"/>
@@ -15372,10 +15367,10 @@
         <v>582</v>
       </c>
       <c r="B583" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C583" s="2" t="s">
         <v>1095</v>
-      </c>
-      <c r="C583" s="2" t="s">
-        <v>1096</v>
       </c>
       <c r="D583" s="2"/>
       <c r="E583" s="2"/>
@@ -15386,10 +15381,10 @@
         <v>583</v>
       </c>
       <c r="B584" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C584" s="2" t="s">
         <v>1097</v>
-      </c>
-      <c r="C584" s="2" t="s">
-        <v>1098</v>
       </c>
       <c r="D584" s="2"/>
       <c r="E584" s="2"/>
@@ -15400,10 +15395,10 @@
         <v>584</v>
       </c>
       <c r="B585" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C585" s="2" t="s">
         <v>1099</v>
-      </c>
-      <c r="C585" s="2" t="s">
-        <v>1100</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" s="2"/>
@@ -15414,7 +15409,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>70</v>
@@ -15428,10 +15423,10 @@
         <v>586</v>
       </c>
       <c r="B587" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C587" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="C587" s="2" t="s">
-        <v>1103</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" s="2"/>
@@ -15442,7 +15437,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>298</v>
@@ -15456,10 +15451,10 @@
         <v>588</v>
       </c>
       <c r="B589" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C589" s="2" t="s">
         <v>1105</v>
-      </c>
-      <c r="C589" s="2" t="s">
-        <v>1106</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" s="2"/>
@@ -15470,10 +15465,10 @@
         <v>589</v>
       </c>
       <c r="B590" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C590" s="2" t="s">
         <v>1107</v>
-      </c>
-      <c r="C590" s="2" t="s">
-        <v>1108</v>
       </c>
       <c r="D590" s="2"/>
       <c r="E590" s="2"/>
@@ -15484,7 +15479,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>201</v>
@@ -15498,10 +15493,10 @@
         <v>591</v>
       </c>
       <c r="B592" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C592" s="2" t="s">
         <v>1110</v>
-      </c>
-      <c r="C592" s="2" t="s">
-        <v>1111</v>
       </c>
       <c r="D592" s="2"/>
       <c r="E592" s="2"/>
@@ -15512,10 +15507,10 @@
         <v>592</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" s="2"/>
@@ -15526,7 +15521,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>98</v>
@@ -15540,10 +15535,10 @@
         <v>594</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D595" s="2"/>
       <c r="E595" s="2"/>
@@ -15554,10 +15549,10 @@
         <v>595</v>
       </c>
       <c r="B596" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C596" s="2" t="s">
         <v>1115</v>
-      </c>
-      <c r="C596" s="2" t="s">
-        <v>1116</v>
       </c>
       <c r="D596" s="2"/>
       <c r="E596" s="2"/>
@@ -15568,10 +15563,10 @@
         <v>596</v>
       </c>
       <c r="B597" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C597" s="2" t="s">
         <v>1117</v>
-      </c>
-      <c r="C597" s="2" t="s">
-        <v>1118</v>
       </c>
       <c r="D597" s="2"/>
       <c r="E597" s="2"/>
@@ -15582,10 +15577,10 @@
         <v>597</v>
       </c>
       <c r="B598" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C598" s="2" t="s">
         <v>1119</v>
-      </c>
-      <c r="C598" s="2" t="s">
-        <v>1120</v>
       </c>
       <c r="D598" s="2"/>
       <c r="E598" s="2"/>
@@ -15596,10 +15591,10 @@
         <v>598</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D599" s="2"/>
       <c r="E599" s="2"/>
@@ -15610,10 +15605,10 @@
         <v>599</v>
       </c>
       <c r="B600" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C600" s="2" t="s">
         <v>1122</v>
-      </c>
-      <c r="C600" s="2" t="s">
-        <v>1123</v>
       </c>
       <c r="D600" s="2"/>
       <c r="E600" s="2"/>
@@ -15624,10 +15619,10 @@
         <v>600</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D601" s="2"/>
       <c r="E601" s="2"/>
@@ -15638,10 +15633,10 @@
         <v>601</v>
       </c>
       <c r="B602" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C602" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="C602" s="2" t="s">
-        <v>1126</v>
       </c>
       <c r="D602" s="2"/>
       <c r="E602" s="2"/>
@@ -15652,10 +15647,10 @@
         <v>602</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D603" s="2"/>
       <c r="E603" s="2"/>
@@ -15666,10 +15661,10 @@
         <v>603</v>
       </c>
       <c r="B604" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C604" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="C604" s="2" t="s">
-        <v>1129</v>
       </c>
       <c r="D604" s="2"/>
       <c r="E604" s="2"/>
@@ -15680,14 +15675,14 @@
         <v>604</v>
       </c>
       <c r="B605" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C605" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="C605" s="2" t="s">
-        <v>1131</v>
       </c>
       <c r="D605" s="2"/>
       <c r="E605" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="F605" s="2"/>
     </row>
@@ -15696,10 +15691,10 @@
         <v>605</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D606" s="2"/>
       <c r="E606" s="2"/>
@@ -15710,14 +15705,14 @@
         <v>606</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>374</v>
       </c>
       <c r="D607" s="2"/>
       <c r="E607" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="F607" s="2"/>
     </row>
@@ -15726,7 +15721,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>380</v>
@@ -15740,10 +15735,10 @@
         <v>608</v>
       </c>
       <c r="B609" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C609" s="2" t="s">
         <v>1137</v>
-      </c>
-      <c r="C609" s="2" t="s">
-        <v>1138</v>
       </c>
       <c r="D609" s="2"/>
       <c r="E609" s="2"/>
@@ -15754,7 +15749,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C610" s="2"/>
       <c r="D610" s="2"/>
@@ -15766,10 +15761,10 @@
         <v>610</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D611" s="2"/>
       <c r="E611" s="2"/>
@@ -15780,10 +15775,10 @@
         <v>611</v>
       </c>
       <c r="B612" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C612" s="2" t="s">
         <v>1141</v>
-      </c>
-      <c r="C612" s="2" t="s">
-        <v>1142</v>
       </c>
       <c r="D612" s="2"/>
       <c r="E612" s="2"/>
@@ -15794,10 +15789,10 @@
         <v>612</v>
       </c>
       <c r="B613" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C613" s="2" t="s">
         <v>1143</v>
-      </c>
-      <c r="C613" s="2" t="s">
-        <v>1144</v>
       </c>
       <c r="D613" s="2"/>
       <c r="E613" s="2"/>
@@ -15808,10 +15803,10 @@
         <v>613</v>
       </c>
       <c r="B614" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C614" s="2" t="s">
         <v>1145</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>1146</v>
       </c>
       <c r="D614" s="2"/>
       <c r="E614" s="2"/>
@@ -15822,10 +15817,10 @@
         <v>614</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D615" s="2"/>
       <c r="E615" s="2"/>
@@ -15836,10 +15831,10 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D616" s="2"/>
       <c r="E616" s="2"/>
@@ -15850,10 +15845,10 @@
         <v>616</v>
       </c>
       <c r="B617" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C617" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="C617" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="D617" s="2"/>
       <c r="E617" s="2"/>
@@ -15864,10 +15859,10 @@
         <v>617</v>
       </c>
       <c r="B618" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C618" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="C618" s="2" t="s">
-        <v>1152</v>
       </c>
       <c r="D618" s="2"/>
       <c r="E618" s="2"/>
@@ -15878,14 +15873,14 @@
         <v>618</v>
       </c>
       <c r="B619" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C619" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="C619" s="2" t="s">
-        <v>1154</v>
       </c>
       <c r="D619" s="2"/>
       <c r="E619" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F619" s="2"/>
     </row>
@@ -15894,7 +15889,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C620" s="2"/>
       <c r="D620" s="2"/>
@@ -15906,13 +15901,13 @@
         <v>620</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D621" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E621" s="2"/>
       <c r="F621" s="2"/>
@@ -15922,7 +15917,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>280</v>
@@ -15936,7 +15931,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C623" s="2" t="s">
         <v>345</v>
@@ -15950,7 +15945,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>21</v>
@@ -15966,7 +15961,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C625" s="2" t="s">
         <v>332</v>
@@ -15980,10 +15975,10 @@
         <v>625</v>
       </c>
       <c r="B626" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C626" s="2" t="s">
         <v>1163</v>
-      </c>
-      <c r="C626" s="2" t="s">
-        <v>1164</v>
       </c>
       <c r="D626" s="2"/>
       <c r="E626" s="2"/>
@@ -15994,13 +15989,13 @@
         <v>626</v>
       </c>
       <c r="B627" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C627" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="C627" s="2" t="s">
+      <c r="D627" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="D627" s="2" t="s">
-        <v>1167</v>
       </c>
       <c r="E627" s="2"/>
       <c r="F627" s="2"/>
@@ -16010,10 +16005,10 @@
         <v>627</v>
       </c>
       <c r="B628" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C628" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>1169</v>
       </c>
       <c r="D628" s="2"/>
       <c r="E628" s="2"/>
@@ -16024,14 +16019,14 @@
         <v>628</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C629" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D629" s="2"/>
       <c r="E629" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="F629" s="2"/>
     </row>
@@ -16040,7 +16035,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>28</v>
@@ -16054,7 +16049,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>255</v>
@@ -16068,10 +16063,10 @@
         <v>631</v>
       </c>
       <c r="B632" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C632" s="2" t="s">
         <v>1174</v>
-      </c>
-      <c r="C632" s="2" t="s">
-        <v>1175</v>
       </c>
       <c r="D632" s="2"/>
       <c r="E632" s="2"/>
@@ -16082,7 +16077,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>215</v>
@@ -16096,7 +16091,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>241</v>
@@ -16110,10 +16105,10 @@
         <v>634</v>
       </c>
       <c r="B635" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C635" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="C635" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="D635" s="2"/>
       <c r="E635" s="2"/>
@@ -16124,10 +16119,10 @@
         <v>635</v>
       </c>
       <c r="B636" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C636" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="C636" s="2" t="s">
-        <v>1181</v>
       </c>
       <c r="D636" s="2"/>
       <c r="E636" s="2"/>
@@ -16138,7 +16133,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C637" s="2"/>
       <c r="D637" s="2"/>
@@ -16150,7 +16145,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C638" s="2"/>
       <c r="D638" s="2"/>
@@ -16162,10 +16157,10 @@
         <v>638</v>
       </c>
       <c r="B639" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C639" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="C639" s="2" t="s">
-        <v>1185</v>
       </c>
       <c r="D639" s="2"/>
       <c r="E639" s="2"/>
@@ -16176,17 +16171,17 @@
         <v>639</v>
       </c>
       <c r="B640" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C640" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="C640" s="2" t="s">
+      <c r="D640" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="D640" s="2" t="s">
-        <v>1188</v>
       </c>
       <c r="E640" s="2"/>
       <c r="F640" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="641" spans="1:6" ht="86" x14ac:dyDescent="0.5">
@@ -16194,10 +16189,10 @@
         <v>640</v>
       </c>
       <c r="B641" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C641" s="2" t="s">
         <v>1190</v>
-      </c>
-      <c r="C641" s="2" t="s">
-        <v>1191</v>
       </c>
       <c r="D641" s="2"/>
       <c r="E641" s="2"/>
@@ -16208,7 +16203,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C642" s="2"/>
       <c r="D642" s="2"/>
@@ -16220,7 +16215,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C643" s="2"/>
       <c r="D643" s="2"/>
@@ -16232,7 +16227,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C644" s="2"/>
       <c r="D644" s="2"/>
@@ -16244,10 +16239,10 @@
         <v>644</v>
       </c>
       <c r="B645" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C645" s="2" t="s">
         <v>1195</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>1196</v>
       </c>
       <c r="D645" s="2"/>
       <c r="E645" s="2"/>
@@ -16258,7 +16253,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>98</v>
@@ -16272,7 +16267,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>88</v>
@@ -16286,14 +16281,14 @@
         <v>647</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>255</v>
       </c>
       <c r="D648" s="2"/>
       <c r="E648" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F648" s="2"/>
     </row>
@@ -16302,7 +16297,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C649" s="2"/>
       <c r="D649" s="2"/>
@@ -16314,7 +16309,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>98</v>
@@ -16328,13 +16323,13 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D651" s="2" t="s">
         <v>1203</v>
-      </c>
-      <c r="C651" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="D651" s="2" t="s">
-        <v>1204</v>
       </c>
       <c r="E651" s="2"/>
       <c r="F651" s="2"/>
@@ -16344,14 +16339,14 @@
         <v>651</v>
       </c>
       <c r="B652" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C652" s="2" t="s">
         <v>1205</v>
-      </c>
-      <c r="C652" s="2" t="s">
-        <v>1206</v>
       </c>
       <c r="D652" s="2"/>
       <c r="E652" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F652" s="2"/>
     </row>
@@ -16360,13 +16355,13 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E653" s="2"/>
       <c r="F653" s="2"/>
@@ -16376,10 +16371,10 @@
         <v>653</v>
       </c>
       <c r="B654" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C654" s="2" t="s">
         <v>1208</v>
-      </c>
-      <c r="C654" s="2" t="s">
-        <v>1209</v>
       </c>
       <c r="D654" s="2"/>
       <c r="E654" s="2"/>
@@ -16390,10 +16385,10 @@
         <v>654</v>
       </c>
       <c r="B655" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C655" s="2" t="s">
         <v>1210</v>
-      </c>
-      <c r="C655" s="2" t="s">
-        <v>1211</v>
       </c>
       <c r="D655" s="2"/>
       <c r="E655" s="2"/>
@@ -16404,7 +16399,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C656" s="2"/>
       <c r="D656" s="2"/>
